--- a/Day_12/Testcase2.xlsx
+++ b/Day_12/Testcase2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\AdvanceSelenium\src\test\resources\DDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E119097-7769-472B-9A7F-8F3F58EC5551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2DC90-92FE-4C39-BEEB-AACD1DB07596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{09751EC3-086D-4D08-B93E-177CB107225B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{09751EC3-086D-4D08-B93E-177CB107225B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
   <si>
     <t>browser</t>
   </si>
@@ -251,6 +252,21 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>EID</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>111</t>
   </si>
 </sst>
 </file>
@@ -982,4 +998,39 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDFC27D-B962-49C1-BCD2-AE5638A19C94}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>